--- a/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Triphammer_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Remedy - Drk Cacoa Essential</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50.12</t>
-        </is>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.12</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>Remedy - Superseed Fuel</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>35.00</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E3" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Just Tea - Honey green</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>25.92</t>
-        </is>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="E4" t="n">
+        <v>25.92</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Martinelli's Apple Juice Squat</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>43.85</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Poppi Soda - Ginger Lime</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>24.07</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>24.07</t>
-        </is>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>24.07</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>San Pellegrino - Limonata (Lemon)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>28.98</t>
-        </is>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>28.98</v>
+      </c>
+      <c r="E7" t="n">
+        <v>28.98</v>
       </c>
     </row>
   </sheetData>

--- a/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Triphammer_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/UNFI/UNFI_Triphammer_20251114.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,27 @@
         <v>28.98</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>0778936</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Seeds - Pumpkin Seeds Raw</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="E8" t="n">
+        <v>65.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
